--- a/artfynd/A 18347-2023 artfynd.xlsx
+++ b/artfynd/A 18347-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131106990</v>
       </c>
       <c r="B2" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 18347-2023 artfynd.xlsx
+++ b/artfynd/A 18347-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131106990</v>
       </c>
       <c r="B2" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 18347-2023 artfynd.xlsx
+++ b/artfynd/A 18347-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131106990</v>
       </c>
       <c r="B2" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 18347-2023 artfynd.xlsx
+++ b/artfynd/A 18347-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131106990</v>
       </c>
       <c r="B2" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 18347-2023 artfynd.xlsx
+++ b/artfynd/A 18347-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131106990</v>
       </c>
       <c r="B2" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 18347-2023 artfynd.xlsx
+++ b/artfynd/A 18347-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131106990</v>
       </c>
       <c r="B2" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 18347-2023 artfynd.xlsx
+++ b/artfynd/A 18347-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131106990</v>
       </c>
       <c r="B2" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 18347-2023 artfynd.xlsx
+++ b/artfynd/A 18347-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131106990</v>
       </c>
       <c r="B2" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 18347-2023 artfynd.xlsx
+++ b/artfynd/A 18347-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131106990</v>
+        <v>131106972</v>
       </c>
       <c r="B2" t="n">
-        <v>79254</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -715,14 +715,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hässjemyran, Mpd</t>
+          <t>Östanskär, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613360</v>
+        <v>613069</v>
       </c>
       <c r="R2" t="n">
-        <v>6938042</v>
+        <v>6938030</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2025_0179</t>
+          <t>2025_0197</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Spridd i området</t>
+          <t>På stående död gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +794,739 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
+          <t>Nellie Gummesson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131106962</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hässjemyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>613282</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6938090</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Indal</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2025_0208</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>David Isaksson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Erik Lagerin</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131106967</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hässjemyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>613243</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6938087</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Indal</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2025_0203</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På torraka på myren</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erik Lagerin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131106990</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hässjemyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>613360</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6938042</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Indal</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2025_0179</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spridd i området</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131106968</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hässjemyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>613240</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6938101</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Indal</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2025_0202</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Torraka på myr</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130723046</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58393</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tjärebläckmon, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>613124</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6938024</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Indal</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>B86</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann, Liam Martin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131106977</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Östanskär, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>613045</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6938103</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Indal</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2025_0192</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spridd förekomst över några kvadratmeter</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Nellie Gummesson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>

--- a/artfynd/A 18347-2023 artfynd.xlsx
+++ b/artfynd/A 18347-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106972</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -918,6 +928,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106962</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1039,6 +1054,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106967</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1169,6 +1189,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106990</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1295,6 +1320,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106968</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1410,6 +1440,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130723046</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1531,8 +1566,22 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106977</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>